--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.01497457974129516</v>
       </c>
       <c r="C2" t="n">
-        <v>93191580</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>93191580</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>63197257</v>
+        <v>4506885</v>
       </c>
       <c r="L2" t="n">
-        <v>35796600</v>
+        <v>2702775</v>
       </c>
       <c r="M2" t="n">
-        <v>8917087</v>
+        <v>699511</v>
       </c>
       <c r="N2" t="n">
-        <v>488571</v>
+        <v>38684</v>
       </c>
       <c r="O2" t="n">
-        <v>5377392</v>
+        <v>418928</v>
       </c>
       <c r="P2" t="n">
-        <v>2198597</v>
+        <v>168244</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999158382415771</v>
+        <v>0.9999752044677734</v>
       </c>
       <c r="R2" t="n">
-        <v>0.858959436416626</v>
+        <v>0.9189581274986267</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7307804226875305</v>
+        <v>0.8271982073783875</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6488089561462402</v>
+        <v>0.7643508911132812</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4787513315677643</v>
+        <v>0.5675552487373352</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7034153342247009</v>
+        <v>0.8217529058456421</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7609390020370483</v>
+        <v>0.8734503388404846</v>
       </c>
       <c r="X2" t="n">
-        <v>93191580</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>93191580</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>61612656</v>
+        <v>4372711</v>
       </c>
       <c r="AG2" t="n">
-        <v>33155928</v>
+        <v>2479581</v>
       </c>
       <c r="AH2" t="n">
-        <v>8100765</v>
+        <v>632335</v>
       </c>
       <c r="AI2" t="n">
-        <v>450676</v>
+        <v>36469</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4945794</v>
+        <v>384092</v>
       </c>
       <c r="AK2" t="n">
-        <v>2068491</v>
+        <v>158512</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8318607211112976</v>
+        <v>0.88556969165802</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6898674368858337</v>
+        <v>0.773880660533905</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5831404328346252</v>
+        <v>0.6827875375747681</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3399609327316284</v>
+        <v>0.412647932767868</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6489853262901306</v>
+        <v>0.7560062408447266</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7135323286056519</v>
+        <v>0.820188045501709</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.003701645093703551</v>
       </c>
       <c r="C3" t="n">
-        <v>2481</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>63197257</v>
+        <v>4506885</v>
       </c>
       <c r="E3" t="n">
-        <v>9381939</v>
+        <v>395377</v>
       </c>
       <c r="F3" t="n">
-        <v>543270</v>
+        <v>11630</v>
       </c>
       <c r="G3" t="n">
-        <v>65066</v>
+        <v>2767</v>
       </c>
       <c r="H3" t="n">
-        <v>54597</v>
+        <v>165</v>
       </c>
       <c r="I3" t="n">
-        <v>9015</v>
+        <v>60</v>
       </c>
       <c r="J3" t="n">
-        <v>147856576</v>
+        <v>9857474</v>
       </c>
       <c r="K3" t="n">
-        <v>157425429</v>
+        <v>10756040</v>
       </c>
       <c r="L3" t="n">
-        <v>179138044</v>
+        <v>12285101</v>
       </c>
       <c r="M3" t="n">
-        <v>222233347</v>
+        <v>14925607</v>
       </c>
       <c r="N3" t="n">
-        <v>239190686</v>
+        <v>15952308</v>
       </c>
       <c r="O3" t="n">
-        <v>231140167</v>
+        <v>15470546</v>
       </c>
       <c r="P3" t="n">
-        <v>237462835</v>
+        <v>15852723</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8627185225486755</v>
+        <v>0.9166105389595032</v>
       </c>
       <c r="S3" t="n">
-        <v>0.73458331823349</v>
+        <v>0.8391915559768677</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6371185779571533</v>
+        <v>0.7528634071350098</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3664170801639557</v>
+        <v>0.4365302324295044</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7030616998672485</v>
+        <v>0.8230671286582947</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7574992775917053</v>
+        <v>0.8703731298446655</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>61612656</v>
+        <v>4372711</v>
       </c>
       <c r="Z3" t="n">
-        <v>10589962</v>
+        <v>509446</v>
       </c>
       <c r="AA3" t="n">
-        <v>745258</v>
+        <v>21836</v>
       </c>
       <c r="AB3" t="n">
-        <v>220526</v>
+        <v>12498</v>
       </c>
       <c r="AC3" t="n">
-        <v>72048</v>
+        <v>346</v>
       </c>
       <c r="AD3" t="n">
-        <v>13175</v>
+        <v>66</v>
       </c>
       <c r="AE3" t="n">
-        <v>147864420</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>155348961</v>
+        <v>10588470</v>
       </c>
       <c r="AG3" t="n">
-        <v>177420139</v>
+        <v>12125205</v>
       </c>
       <c r="AH3" t="n">
-        <v>221269184</v>
+        <v>14847493</v>
       </c>
       <c r="AI3" t="n">
-        <v>238847632</v>
+        <v>15929874</v>
       </c>
       <c r="AJ3" t="n">
-        <v>230732449</v>
+        <v>15437454</v>
       </c>
       <c r="AK3" t="n">
-        <v>237323105</v>
+        <v>15842348</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8410868048667908</v>
+        <v>0.8893222212791443</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6803939938545227</v>
+        <v>0.7698915004730225</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5787930488586426</v>
+        <v>0.6805638074874878</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3379966914653778</v>
+        <v>0.4115350246429443</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6466328501701355</v>
+        <v>0.7546249032020569</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7126728892326355</v>
+        <v>0.8200268149375916</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0454970835507619</v>
       </c>
       <c r="C4" t="n">
-        <v>959</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>9571981</v>
+        <v>376031</v>
       </c>
       <c r="E4" t="n">
-        <v>35796600</v>
+        <v>2702775</v>
       </c>
       <c r="F4" t="n">
-        <v>2748841</v>
+        <v>131501</v>
       </c>
       <c r="G4" t="n">
-        <v>114575</v>
+        <v>3936</v>
       </c>
       <c r="H4" t="n">
-        <v>431432</v>
+        <v>6051</v>
       </c>
       <c r="I4" t="n">
-        <v>66096</v>
+        <v>388</v>
       </c>
       <c r="J4" t="n">
-        <v>7844</v>
+        <v>154</v>
       </c>
       <c r="K4" t="n">
-        <v>10376946</v>
+        <v>397457</v>
       </c>
       <c r="L4" t="n">
-        <v>13187472</v>
+        <v>564610</v>
       </c>
       <c r="M4" t="n">
-        <v>4826692</v>
+        <v>215659</v>
       </c>
       <c r="N4" t="n">
-        <v>531940</v>
+        <v>29475</v>
       </c>
       <c r="O4" t="n">
-        <v>2267298</v>
+        <v>90870</v>
       </c>
       <c r="P4" t="n">
-        <v>690724</v>
+        <v>24376</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999579191207886</v>
+        <v>0.9999876022338867</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8608348369598389</v>
+        <v>0.9177828431129456</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7326769232749939</v>
+        <v>0.8331517577171326</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6429105997085571</v>
+        <v>0.7585636377334595</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4151188433170319</v>
+        <v>0.4934938549995422</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7032384872436523</v>
+        <v>0.8224095106124878</v>
       </c>
       <c r="W4" t="n">
-        <v>0.759215235710144</v>
+        <v>0.871908962726593</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>11434669</v>
+        <v>536843</v>
       </c>
       <c r="Z4" t="n">
-        <v>33155928</v>
+        <v>2479581</v>
       </c>
       <c r="AA4" t="n">
-        <v>3303290</v>
+        <v>178536</v>
       </c>
       <c r="AB4" t="n">
-        <v>224857</v>
+        <v>11674</v>
       </c>
       <c r="AC4" t="n">
-        <v>527234</v>
+        <v>12933</v>
       </c>
       <c r="AD4" t="n">
-        <v>84506</v>
+        <v>1122</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>12453414</v>
+        <v>565027</v>
       </c>
       <c r="AG4" t="n">
-        <v>14905377</v>
+        <v>724506</v>
       </c>
       <c r="AH4" t="n">
-        <v>5790855</v>
+        <v>293773</v>
       </c>
       <c r="AI4" t="n">
-        <v>874994</v>
+        <v>51909</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2675016</v>
+        <v>123962</v>
       </c>
       <c r="AK4" t="n">
-        <v>830454</v>
+        <v>34751</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8364483714103699</v>
+        <v>0.8874420523643494</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6850979924201965</v>
+        <v>0.7718809247016907</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5809586048126221</v>
+        <v>0.6816738843917847</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3389759659767151</v>
+        <v>0.4120906889438629</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6478069424629211</v>
+        <v>0.7553150057792664</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7131023406982422</v>
+        <v>0.8201074004173279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1473</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>570541</v>
+        <v>12199</v>
       </c>
       <c r="E5" t="n">
-        <v>3046579</v>
+        <v>150657</v>
       </c>
       <c r="F5" t="n">
-        <v>8917087</v>
+        <v>699511</v>
       </c>
       <c r="G5" t="n">
-        <v>192417</v>
+        <v>12358</v>
       </c>
       <c r="H5" t="n">
-        <v>1111010</v>
+        <v>51943</v>
       </c>
       <c r="I5" t="n">
-        <v>156854</v>
+        <v>2447</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10056368</v>
+        <v>410018</v>
       </c>
       <c r="L5" t="n">
-        <v>12933884</v>
+        <v>517914</v>
       </c>
       <c r="M5" t="n">
-        <v>5078874</v>
+        <v>229623</v>
       </c>
       <c r="N5" t="n">
-        <v>844803</v>
+        <v>49933</v>
       </c>
       <c r="O5" t="n">
-        <v>2271143</v>
+        <v>90056</v>
       </c>
       <c r="P5" t="n">
-        <v>703844</v>
+        <v>25057</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999674558639526</v>
+        <v>0.9999904036521912</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9152341485023499</v>
+        <v>0.9497538805007935</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8916378021240234</v>
+        <v>0.9326386451721191</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9589076042175293</v>
+        <v>0.9722917675971985</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9942886829376221</v>
+        <v>0.9950587153434753</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9811726808547974</v>
+        <v>0.9887416362762451</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9942147731781006</v>
+        <v>0.9969239830970764</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>722146</v>
+        <v>16840</v>
       </c>
       <c r="Z5" t="n">
-        <v>3435003</v>
+        <v>189907</v>
       </c>
       <c r="AA5" t="n">
-        <v>8100765</v>
+        <v>632335</v>
       </c>
       <c r="AB5" t="n">
-        <v>240911</v>
+        <v>15586</v>
       </c>
       <c r="AC5" t="n">
-        <v>1305586</v>
+        <v>69220</v>
       </c>
       <c r="AD5" t="n">
-        <v>191550</v>
+        <v>5246</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>11640969</v>
+        <v>544192</v>
       </c>
       <c r="AG5" t="n">
-        <v>15574556</v>
+        <v>741108</v>
       </c>
       <c r="AH5" t="n">
-        <v>5895196</v>
+        <v>296799</v>
       </c>
       <c r="AI5" t="n">
-        <v>882698</v>
+        <v>52148</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2702741</v>
+        <v>124892</v>
       </c>
       <c r="AK5" t="n">
-        <v>833950</v>
+        <v>34789</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9000465273857117</v>
+        <v>0.9309775233268738</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8735566139221191</v>
+        <v>0.9088004231452942</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9515214562416077</v>
+        <v>0.9632509350776672</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9927083849906921</v>
+        <v>0.9935249090194702</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9776908159255981</v>
+        <v>0.9845147728919983</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.993095338344574</v>
+        <v>0.9956727623939514</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1976</v>
+        <v>79</v>
       </c>
       <c r="D6" t="n">
-        <v>167763</v>
+        <v>9172</v>
       </c>
       <c r="E6" t="n">
-        <v>233805</v>
+        <v>13093</v>
       </c>
       <c r="F6" t="n">
-        <v>268417</v>
+        <v>17004</v>
       </c>
       <c r="G6" t="n">
-        <v>488571</v>
+        <v>38684</v>
       </c>
       <c r="H6" t="n">
-        <v>147220</v>
+        <v>9631</v>
       </c>
       <c r="I6" t="n">
-        <v>25622</v>
+        <v>954</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>202552</v>
+        <v>11247</v>
       </c>
       <c r="Z6" t="n">
-        <v>235826</v>
+        <v>11948</v>
       </c>
       <c r="AA6" t="n">
-        <v>248399</v>
+        <v>17047</v>
       </c>
       <c r="AB6" t="n">
-        <v>450676</v>
+        <v>36469</v>
       </c>
       <c r="AC6" t="n">
-        <v>166037</v>
+        <v>10586</v>
       </c>
       <c r="AD6" t="n">
-        <v>29884</v>
+        <v>1320</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>606</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>62026</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>474015</v>
+        <v>5230</v>
       </c>
       <c r="F7" t="n">
-        <v>1161469</v>
+        <v>54311</v>
       </c>
       <c r="G7" t="n">
-        <v>139890</v>
+        <v>9956</v>
       </c>
       <c r="H7" t="n">
-        <v>5377392</v>
+        <v>418928</v>
       </c>
       <c r="I7" t="n">
-        <v>433137</v>
+        <v>20527</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>86279</v>
+        <v>46</v>
       </c>
       <c r="Z7" t="n">
-        <v>579778</v>
+        <v>12624</v>
       </c>
       <c r="AA7" t="n">
-        <v>1361524</v>
+        <v>73845</v>
       </c>
       <c r="AB7" t="n">
-        <v>163821</v>
+        <v>11380</v>
       </c>
       <c r="AC7" t="n">
-        <v>4945794</v>
+        <v>384092</v>
       </c>
       <c r="AD7" t="n">
-        <v>511339</v>
+        <v>26997</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>4635</v>
+        <v>34</v>
       </c>
       <c r="E8" t="n">
-        <v>51134</v>
+        <v>253</v>
       </c>
       <c r="F8" t="n">
-        <v>104695</v>
+        <v>1213</v>
       </c>
       <c r="G8" t="n">
-        <v>19992</v>
+        <v>458</v>
       </c>
       <c r="H8" t="n">
-        <v>523039</v>
+        <v>23080</v>
       </c>
       <c r="I8" t="n">
-        <v>2198597</v>
+        <v>168244</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7768</v>
+        <v>51</v>
       </c>
       <c r="Z8" t="n">
-        <v>64808</v>
+        <v>581</v>
       </c>
       <c r="AA8" t="n">
-        <v>132384</v>
+        <v>2509</v>
       </c>
       <c r="AB8" t="n">
-        <v>24879</v>
+        <v>771</v>
       </c>
       <c r="AC8" t="n">
-        <v>604111</v>
+        <v>30877</v>
       </c>
       <c r="AD8" t="n">
-        <v>2068491</v>
+        <v>158512</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
